--- a/preview/ci-artifacts/latest/policy-governance-events.xlsx
+++ b/preview/ci-artifacts/latest/policy-governance-events.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="41">
   <si>
     <t>event_id</t>
   </si>

--- a/preview/ci-artifacts/latest/policy-governance-events.xlsx
+++ b/preview/ci-artifacts/latest/policy-governance-events.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="46">
   <si>
     <t>event_id</t>
   </si>
